--- a/data/argentina/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/argentina/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,35 +577,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>noM4eJv9</t>
+          <t>fotMKZ7K</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45506.83333333334</v>
+        <v>45513.625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">espinoza f 
+          <t xml:space="preserve">mastrangelo h 
   arg </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio marcelo bielsa
-  rosario </t>
+          <t xml:space="preserve">estadio guillermo laza
+  buenos aires </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>42000</v>
+        <v>3000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>6gMiRHVj</t>
+          <t>2iZ4q0z6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>p2SkCHXs</t>
+          <t>Y9yh1J7G</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -630,87 +630,73 @@
           <t>liga profesional</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>4QmJ2LNc</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>175</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T2" t="n">
-        <v>59</v>
-      </c>
-      <c r="U2" t="n">
-        <v>575000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>75</v>
-      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>GIb40wNM</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="X2" t="n">
-        <v>176</v>
+        <v>179.3333333333333</v>
       </c>
       <c r="Y2" t="n">
         <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AA2" t="n">
-        <v>69</v>
+        <v>414</v>
       </c>
       <c r="AB2" t="n">
-        <v>1900000</v>
+        <v>13275000</v>
       </c>
       <c r="AC2" t="n">
-        <v>72</v>
+        <v>444</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nkx6zI2q</t>
+          <t>YHCv8dOE</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45507.625</v>
+        <v>45513.6875</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">gariano a 
+          <t xml:space="preserve">trucco s 
   arg </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio malvinas argentinas
-  mendoza </t>
+          <t xml:space="preserve">claudio fabian tapia
+  barracas </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>42000</v>
+        <v>4400</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>tUAxIm6l</t>
+          <t>hW08cP6J</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>QuxS0ahA</t>
+          <t>bkDdeAvA</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -735,83 +721,77 @@
           <t>liga profesional</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>xd3lGq3F</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Amzaty2s</t>
+        </is>
+      </c>
       <c r="P3" t="n">
-        <v>23.66666666666667</v>
+        <v>22</v>
       </c>
       <c r="Q3" t="n">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>206</v>
+        <v>63</v>
       </c>
       <c r="U3" t="n">
-        <v>6100000</v>
+        <v>1000000</v>
       </c>
       <c r="V3" t="n">
-        <v>220</v>
-      </c>
-      <c r="W3" t="n">
-        <v>29</v>
-      </c>
-      <c r="X3" t="n">
-        <v>169</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>68</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>68</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pdWqnF1e</t>
+          <t>llkWcC07</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45507.625</v>
+        <v>45513.79166666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">lamolina n 
+          <t xml:space="preserve">herrera d 
   arg </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio jose amalfitani
-  buenos aires </t>
+          <t xml:space="preserve">estadio julio cesar villagra
+  cordoba </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>49540</v>
+        <v>34830</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>UsCR8gFd</t>
+          <t>Amzaty2s</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gdfv0Zsh</t>
+          <t>lr2YMkTK</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -838,89 +818,75 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>ju1xJoJd</t>
+          <t>bkDdeAvA</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>zoYzAZW6</t>
+          <t>SAk2Byml</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>25</v>
+        <v>26.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>278</v>
+        <v>146</v>
       </c>
       <c r="U4" t="n">
-        <v>8950000</v>
+        <v>7100000</v>
       </c>
       <c r="V4" t="n">
-        <v>298</v>
-      </c>
-      <c r="W4" t="n">
-        <v>27</v>
-      </c>
-      <c r="X4" t="n">
-        <v>179.6</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>356</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>358</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>vq1qlyXr</t>
+          <t>hMeNaYVf</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45507.71875</v>
+        <v>45513.875</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">herrera d 
+          <t xml:space="preserve">arasa n 
   arg </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio mario alberto kempes
-  cordoba </t>
+          <t xml:space="preserve">estadio juan domingo peron
+  avellaneda </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>57000</v>
+        <v>61000</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>bkDdeAvA</t>
+          <t>OhapHPm9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8G45bXRA</t>
+          <t>jiDN9Zaj</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -947,75 +913,85 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Amzaty2s</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Amzaty2s</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+          <t>UVatI5Y2</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>178</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>74</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>74</v>
+      </c>
       <c r="W5" t="n">
-        <v>33</v>
+        <v>22.4</v>
       </c>
       <c r="X5" t="n">
-        <v>175</v>
+        <v>178.2</v>
       </c>
       <c r="Y5" t="n">
         <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA5" t="n">
-        <v>67</v>
+        <v>324</v>
       </c>
       <c r="AB5" t="n">
-        <v>500000</v>
+        <v>7200000</v>
       </c>
       <c r="AC5" t="n">
-        <v>67</v>
+        <v>367</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>U9B9fwfF</t>
+          <t>trGn6zgR</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45507.80208333334</v>
+        <v>45514.60416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">mastrangelo h 
+          <t xml:space="preserve">rey hilfer l 
   arg </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio libertadores de america
-  avellaneda </t>
+          <t xml:space="preserve">estadio pedro bidegain
+  buenos aires </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>48069</v>
+        <v>47964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UVatI5Y2</t>
+          <t>ju1xJoJd</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ju1xJoJd</t>
+          <t>KpqpxWko</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1042,89 +1018,85 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>OhapHPm9</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
           <t>xd3lGq3F</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>23</v>
+        <v>27.66666666666667</v>
       </c>
       <c r="Q6" t="n">
-        <v>169</v>
+        <v>182.6666666666667</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>70</v>
+        <v>208</v>
       </c>
       <c r="U6" t="n">
-        <v>3200000</v>
+        <v>8800000</v>
       </c>
       <c r="V6" t="n">
-        <v>77</v>
+        <v>229</v>
       </c>
       <c r="W6" t="n">
-        <v>27.66666666666667</v>
+        <v>24</v>
       </c>
       <c r="X6" t="n">
-        <v>182.6666666666667</v>
+        <v>181</v>
       </c>
       <c r="Y6" t="n">
         <v>1</v>
       </c>
       <c r="Z6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>208</v>
+        <v>62</v>
       </c>
       <c r="AB6" t="n">
-        <v>8800000</v>
+        <v>625000</v>
       </c>
       <c r="AC6" t="n">
-        <v>229</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KvUIXFn2</t>
+          <t>badJ0EGl</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45507.85416666666</v>
+        <v>45514.6875</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">tello f 
+          <t xml:space="preserve">ramirez n 
   arg </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio tomas adolfo duco
-  buenos aires </t>
+          <t xml:space="preserve">estadio gigante de arroyito
+  rosario </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>48314</v>
+        <v>46955</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>xd3lGq3F</t>
+          <t>4QmJ2LNc</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>OhapHPm9</t>
+          <t>6gMiRHVj</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1151,26 +1123,40 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>ju1xJoJd</t>
+          <t>6gMiRHVj</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>UVatI5Y2</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
+          <t>4QmJ2LNc</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>182.75</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>281</v>
+      </c>
+      <c r="U7" t="n">
+        <v>7400000</v>
+      </c>
+      <c r="V7" t="n">
+        <v>293</v>
+      </c>
       <c r="W7" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="X7" t="n">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="Y7" t="n">
         <v>1</v>
@@ -1179,47 +1165,47 @@
         <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="AB7" t="n">
-        <v>2900000</v>
+        <v>575000</v>
       </c>
       <c r="AC7" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bPuAZyIk</t>
+          <t>2iHr7GwL</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45508.625</v>
+        <v>45514.78125</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ramirez n 
+          <t xml:space="preserve">tello f 
   arg </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio eva peron
-  junin </t>
+          <t xml:space="preserve">estadio juan bautista gargantini
+  mendoza </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KQ6kGfyc</t>
+          <t>Eg51aDC4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Amzaty2s</t>
+          <t>hMrWAFH0</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1244,21 +1230,17 @@
           <t>liga profesional</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>80MMdBdN</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>bkDdeAvA</t>
+          <t>EVqSBe2f</t>
         </is>
       </c>
       <c r="P8" t="n">
         <v>27</v>
       </c>
       <c r="Q8" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1267,7 +1249,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="U8" t="n">
         <v>975000</v>
@@ -1275,46 +1257,60 @@
       <c r="V8" t="n">
         <v>67</v>
       </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>26</v>
+      </c>
+      <c r="X8" t="n">
+        <v>178</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>72</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>tlVEYeXe</t>
+          <t>WCfRbho1</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45508.625</v>
+        <v>45514.85416666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">echavarria p 
+          <t xml:space="preserve">echenique f 
   arg </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio 15 de abril
-  santa fe </t>
+          <t xml:space="preserve">estadio monumental
+  buenos aires </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>27358</v>
+        <v>84567</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>lr2YMkTK</t>
+          <t>EVqSBe2f</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>EVqSBe2f</t>
+          <t>xd3lGq3F</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1341,75 +1337,75 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>SAk2Byml</t>
+          <t>hMrWAFH0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>hMrWAFH0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="n">
-        <v>30</v>
-      </c>
-      <c r="X9" t="n">
-        <v>172</v>
-      </c>
-      <c r="Y9" t="n">
+          <t>ju1xJoJd</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>172.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="Z9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>5500000</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>75</v>
-      </c>
+      <c r="T9" t="n">
+        <v>148</v>
+      </c>
+      <c r="U9" t="n">
+        <v>8600000</v>
+      </c>
+      <c r="V9" t="n">
+        <v>148</v>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>xzFHhHOR</t>
+          <t>vJVmoZG1</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45508.72916666666</v>
+        <v>45515.625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">echenique f 
+          <t xml:space="preserve">espinoza f 
   arg </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio alberto j  armando
-  buenos aires </t>
+          <t xml:space="preserve">estadio unico madre de ciudades
+  santiago del estero </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>57200</v>
+        <v>42000</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>hMrWAFH0</t>
+          <t>0dHZReql</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>hW08cP6J</t>
+          <t>Gdfv0Zsh</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1434,21 +1430,17 @@
           <t>liga profesional</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>EVqSBe2f</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>xd3lGq3F</t>
+          <t>zoYzAZW6</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q10" t="n">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1457,68 +1449,68 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="U10" t="n">
-        <v>2500000</v>
+        <v>650000</v>
       </c>
       <c r="V10" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="W10" t="n">
-        <v>22</v>
+        <v>26.5</v>
       </c>
       <c r="X10" t="n">
-        <v>172</v>
+        <v>179.5</v>
       </c>
       <c r="Y10" t="n">
         <v>1</v>
       </c>
       <c r="Z10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA10" t="n">
-        <v>63</v>
+        <v>146</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000000</v>
+        <v>6700000</v>
       </c>
       <c r="AC10" t="n">
-        <v>72</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>rDFDgc9L</t>
+          <t>fRDz9x98</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45508.83333333334</v>
+        <v>45515.625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">arasa n 
+          <t xml:space="preserve">balino j 
   arg </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio monumental jose fierro
-  tucuman </t>
+          <t xml:space="preserve">estadio presidente peron
+  cordoba </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>35200</v>
+        <v>26000</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>KpqpxWko</t>
+          <t>8G45bXRA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Eg51aDC4</t>
+          <t>80MMdBdN</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1543,13 +1535,17 @@
           <t>liga profesional</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Amzaty2s</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="Q11" t="n">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1558,44 +1554,44 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="U11" t="n">
-        <v>625000</v>
+        <v>500000</v>
       </c>
       <c r="V11" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="W11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="X11" t="n">
-        <v>163</v>
+        <v>177.8</v>
       </c>
       <c r="Y11" t="n">
         <v>1</v>
       </c>
       <c r="Z11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA11" t="n">
-        <v>67</v>
+        <v>336</v>
       </c>
       <c r="AB11" t="n">
-        <v>975000</v>
+        <v>5300000</v>
       </c>
       <c r="AC11" t="n">
-        <v>67</v>
+        <v>347</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>U9kvubfS</t>
+          <t>hMZipgW7</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45508.83333333334</v>
+        <v>45515.72916666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1605,21 +1601,21 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ciudad de lanus – nestor diaz perez
-  lanus </t>
+          <t xml:space="preserve">estadio florencio sola
+  buenos aires </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>47090</v>
+        <v>34902</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Y9yh1J7G</t>
+          <t>GIb40wNM</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>nkwO1uw4</t>
+          <t>UsCR8gFd</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1646,75 +1642,89 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>GIb40wNM</t>
+          <t>Y9yh1J7G</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>80MMdBdN</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+          <t>ju1xJoJd</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>128</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2125000</v>
+      </c>
+      <c r="V12" t="n">
+        <v>142</v>
+      </c>
       <c r="W12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="X12" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Y12" t="n">
         <v>1</v>
       </c>
       <c r="Z12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA12" t="n">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000000</v>
+        <v>2150000</v>
       </c>
       <c r="AC12" t="n">
-        <v>67</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>jJjztvuM</t>
+          <t>nPhF1f1r</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45509.60416666666</v>
+        <v>45515.83333333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">rey hilfer l 
+          <t xml:space="preserve">zunino s 
   arg </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio guillermo laza
-  buenos aires </t>
+          <t xml:space="preserve">estadio jorge luis hirschi
+  la plata </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3000</v>
+        <v>32530</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2iZ4q0z6</t>
+          <t>p2SkCHXs</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0dHZReql</t>
+          <t>UVatI5Y2</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1740,54 +1750,81 @@
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>OhapHPm9</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>176</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>69</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="V13" t="n">
+        <v>72</v>
+      </c>
+      <c r="W13" t="n">
+        <v>19</v>
+      </c>
+      <c r="X13" t="n">
+        <v>174</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>8fN0daP2</t>
+          <t>trxILFhE</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45509.70833333334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zunino s 
-  arg </t>
-        </is>
-      </c>
+        <v>45516.79166666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio juan carmelo zerillo
-  la plata </t>
+          <t xml:space="preserve">estadio jose dellagiovanna
+  buenos aires </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>21500</v>
+        <v>26282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>jiDN9Zaj</t>
+          <t>nkwO1uw4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4QmJ2LNc</t>
+          <t>tUAxIm6l</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1812,12 +1849,12 @@
           <t>liga profesional</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>6gMiRHVj</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>80MMdBdN</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
@@ -1836,45 +1873,40 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>65Xumenk</t>
+          <t>Y9EiyTMr</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45509.83333333334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">penel a 
-  arg </t>
-        </is>
-      </c>
+        <v>45518.79166666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ciudad de vicente lopez
-  buenos aires </t>
+          <t xml:space="preserve">estadio libertadores de america
+  avellaneda </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>28530</v>
+        <v>48069</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>80MMdBdN</t>
+          <t>QuxS0ahA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>GIb40wNM</t>
+          <t>xd3lGq3F</t>
         </is>
       </c>
       <c r="H15" t="n">
         <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>2024</v>
@@ -1886,13 +1918,13 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>liga profesional</t>
+          <t>copa argentina</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Y9yh1J7G</t>
+          <t>ju1xJoJd</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1913,40 +1945,40 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SvlzcWFD</t>
+          <t>fgvPVMI8</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45512.625</v>
+        <v>45519.70833333334</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio diego armando maradona
-  buenos aires </t>
+          <t xml:space="preserve">estadio centenario ciudad de quilmes
+  quilmes </t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>26000</v>
+        <v>30200</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>QuxS0ahA</t>
+          <t>ABogdBtb</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>KQ6kGfyc</t>
+          <t>GIb40wNM</t>
         </is>
       </c>
       <c r="H16" t="n">
         <v>6</v>
       </c>
       <c r="I16" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>2024</v>
@@ -1958,13 +1990,13 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>liga profesional</t>
+          <t>copa argentina</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>80MMdBdN</t>
+          <t>Y9yh1J7G</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -1982,82 +2014,6 @@
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ngdGLTFj</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45510.88194444445</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio libertadores de america
-  avellaneda </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>48069</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ju1xJoJd</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>UsCR8gFd</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>6</v>
-      </c>
-      <c r="I17" t="n">
-        <v>64</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>argentina</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>copa argentina</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>xd3lGq3F</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>ju1xJoJd</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
